--- a/public/templates/BF_Prime_UNITED_template.xlsx
+++ b/public/templates/BF_Prime_UNITED_template.xlsx
@@ -11,15 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Invoice</t>
   </si>
   <si>
     <t>Pay Period</t>
-  </si>
-  <si>
-    <t>11/4/2025-11/10/2025</t>
   </si>
   <si>
     <t>Driver name</t>
@@ -104,24 +101,6 @@
   </si>
   <si>
     <t>Amount</t>
-  </si>
-  <si>
-    <t>Cargo Insurance</t>
-  </si>
-  <si>
-    <t>Trailer + Insurance</t>
-  </si>
-  <si>
-    <t>ELD</t>
-  </si>
-  <si>
-    <t>Pre-Pass</t>
-  </si>
-  <si>
-    <t>Truck Payment</t>
-  </si>
-  <si>
-    <t>Truck Insurance</t>
   </si>
   <si>
     <t>Total Deductions</t>
@@ -212,7 +191,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +208,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -727,19 +712,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="7" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="7" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="27" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf borderId="8" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -776,14 +761,14 @@
     <xf borderId="3" fillId="2" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="28" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="29" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="30" fillId="4" fontId="11" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="30" fillId="5" fontId="11" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="31" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1084,9 +1069,7 @@
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7">
-        <v>7892.0</v>
-      </c>
+      <c r="C2" s="7"/>
       <c r="D2" s="8"/>
       <c r="E2" s="9"/>
       <c r="F2" s="10"/>
@@ -1113,9 +1096,7 @@
     </row>
     <row r="3" ht="21.0" customHeight="1">
       <c r="A3" s="11"/>
-      <c r="B3" s="12">
-        <v>45981.0</v>
-      </c>
+      <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14"/>
       <c r="E3" s="9"/>
@@ -1145,9 +1126,7 @@
       <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="16"/>
       <c r="C4" s="13"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1230,12 +1209,12 @@
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
       <c r="D7" s="21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="23"/>
@@ -1262,12 +1241,12 @@
     </row>
     <row r="8" ht="21.0" customHeight="1">
       <c r="A8" s="25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="26"/>
       <c r="C8" s="27"/>
       <c r="D8" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="28"/>
@@ -1297,7 +1276,7 @@
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
       <c r="D9" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="28"/>
@@ -1379,30 +1358,30 @@
     </row>
     <row r="12" ht="21.0" customHeight="1">
       <c r="A12" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>9</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>10</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="J12" s="42" t="s">
         <v>14</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>15</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="4"/>
@@ -1646,7 +1625,7 @@
       <c r="E20" s="11"/>
       <c r="F20" s="17"/>
       <c r="G20" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="51"/>
       <c r="I20" s="52">
@@ -1676,7 +1655,7 @@
     </row>
     <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="54"/>
       <c r="C21" s="5"/>
@@ -1706,34 +1685,34 @@
     </row>
     <row r="22" ht="21.0" customHeight="1">
       <c r="A22" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="C22" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="D22" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="56" t="s">
+      <c r="E22" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="F22" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="G22" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="56" t="s">
+      <c r="H22" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="56" t="s">
+      <c r="I22" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="56" t="s">
+      <c r="J22" s="58" t="s">
         <v>26</v>
-      </c>
-      <c r="J22" s="58" t="s">
-        <v>27</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="4"/>
@@ -2098,7 +2077,7 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
       <c r="I35" s="62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J35" s="63">
         <f>SUM(J23:J34)</f>
@@ -2180,7 +2159,7 @@
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="69"/>
       <c r="B38" s="70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C38" s="71"/>
       <c r="D38" s="72"/>
@@ -2189,10 +2168,10 @@
       <c r="G38" s="74"/>
       <c r="H38" s="75"/>
       <c r="I38" s="76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" s="57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="4"/>
@@ -2213,19 +2192,15 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="77"/>
-      <c r="B39" s="78" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="79"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J39" s="82"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="81"/>
       <c r="K39" s="5"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -2245,19 +2220,15 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="77"/>
-      <c r="B40" s="78" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J40" s="82"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="81"/>
       <c r="K40" s="5"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -2277,19 +2248,15 @@
     </row>
     <row r="41" ht="21.0" customHeight="1">
       <c r="A41" s="77"/>
-      <c r="B41" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J41" s="82"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="81"/>
       <c r="K41" s="5"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -2309,19 +2276,15 @@
     </row>
     <row r="42" ht="21.0" customHeight="1">
       <c r="A42" s="77"/>
-      <c r="B42" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J42" s="82"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="81"/>
       <c r="K42" s="5"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -2341,19 +2304,15 @@
     </row>
     <row r="43" ht="21.0" customHeight="1">
       <c r="A43" s="77"/>
-      <c r="B43" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
       <c r="E43" s="83"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J43" s="82"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="81"/>
       <c r="K43" s="5"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -2373,19 +2332,15 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="77"/>
-      <c r="B44" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="80"/>
-      <c r="D44" s="80"/>
-      <c r="E44" s="80"/>
-      <c r="F44" s="80"/>
-      <c r="G44" s="80"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J44" s="82"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="81"/>
       <c r="K44" s="5"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -2405,17 +2360,15 @@
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="77"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="80"/>
-      <c r="E45" s="80"/>
-      <c r="F45" s="80"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J45" s="82"/>
+      <c r="B45" s="78"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="79"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="81"/>
       <c r="K45" s="5"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -2435,17 +2388,15 @@
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="77"/>
-      <c r="B46" s="80"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="80"/>
-      <c r="F46" s="80"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J46" s="82"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="79"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="81"/>
       <c r="K46" s="5"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -2465,17 +2416,15 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="77"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="81">
-        <v>45971.0</v>
-      </c>
-      <c r="J47" s="82"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="78"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="81"/>
       <c r="K47" s="5"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -2503,7 +2452,7 @@
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="62" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J48" s="84">
         <f>SUM(J39:J47)</f>
@@ -2585,7 +2534,7 @@
     <row r="51" ht="21.0" customHeight="1">
       <c r="A51" s="87"/>
       <c r="B51" s="28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C51" s="71"/>
       <c r="D51" s="72"/>
@@ -2594,10 +2543,10 @@
       <c r="G51" s="89"/>
       <c r="H51" s="89"/>
       <c r="I51" s="90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51" s="91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="4"/>
@@ -2646,13 +2595,13 @@
     </row>
     <row r="53" ht="21.0" customHeight="1">
       <c r="A53" s="77"/>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="80"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="78"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="78"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="78"/>
+      <c r="F53" s="78"/>
+      <c r="G53" s="78"/>
+      <c r="H53" s="79"/>
       <c r="I53" s="94"/>
       <c r="J53" s="95"/>
       <c r="K53" s="5"/>
@@ -2674,13 +2623,13 @@
     </row>
     <row r="54" ht="21.0" customHeight="1">
       <c r="A54" s="77"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="78"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="78"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
       <c r="I54" s="94"/>
       <c r="J54" s="95"/>
       <c r="K54" s="5"/>
@@ -2710,7 +2659,7 @@
       <c r="G55" s="35"/>
       <c r="H55" s="35"/>
       <c r="I55" s="62" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J55" s="53">
         <f>SUM(J52:J54)</f>
@@ -2883,7 +2832,7 @@
       <c r="G61" s="35"/>
       <c r="H61" s="35"/>
       <c r="I61" s="99" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J61" s="100"/>
       <c r="K61" s="5"/>
